--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.05001319410032</v>
+        <v>6.183127144041303</v>
       </c>
       <c r="D2" t="n">
-        <v>36.92851267243449</v>
+        <v>6.000883309270606</v>
       </c>
       <c r="E2" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F2" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.31367637509092</v>
+        <v>2.488472410952275</v>
       </c>
       <c r="D3" t="n">
-        <v>16.03245156209711</v>
+        <v>2.60527337884078</v>
       </c>
       <c r="E3" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F3" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.83186486416426</v>
+        <v>3.060178040426692</v>
       </c>
       <c r="D4" t="n">
-        <v>18.83202699274907</v>
+        <v>3.060204386321724</v>
       </c>
       <c r="E4" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F4" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.125339433374316</v>
+        <v>1.482867657923326</v>
       </c>
       <c r="D5" t="n">
-        <v>8.60919320282022</v>
+        <v>1.398993895458286</v>
       </c>
       <c r="E5" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F5" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.41291055856644</v>
+        <v>5.592097965767047</v>
       </c>
       <c r="D6" t="n">
-        <v>34.86929458069751</v>
+        <v>5.666260369363345</v>
       </c>
       <c r="E6" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F6" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.01352803979045</v>
+        <v>5.202198306465949</v>
       </c>
       <c r="D7" t="n">
-        <v>32.98150170895521</v>
+        <v>5.359494027705223</v>
       </c>
       <c r="E7" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F7" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.210325467369</v>
+        <v>3.446677888447463</v>
       </c>
       <c r="D8" t="n">
-        <v>22.85936313571708</v>
+        <v>3.714646509554025</v>
       </c>
       <c r="E8" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F8" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.80424442738954</v>
+        <v>5.330689719450801</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39396737366859</v>
+        <v>5.589019698221147</v>
       </c>
       <c r="E9" t="n">
-        <v>9.790625211750292</v>
+        <v>1.590976596909423</v>
       </c>
       <c r="F9" t="n">
-        <v>9.871392628304243</v>
+        <v>1.604101302099439</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
